--- a/member_deposit/2026-08-18_会员沉淀分析.xlsx
+++ b/member_deposit/2026-08-18_会员沉淀分析.xlsx
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23885</v>
+        <v>24094</v>
       </c>
       <c r="C2" t="n">
-        <v>23847</v>
+        <v>24056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+139</t>
+          <t>+348</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25157</v>
+        <v>25531</v>
       </c>
       <c r="C3" t="n">
-        <v>25156</v>
+        <v>25530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+302</t>
+          <t>+676</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51684</v>
+        <v>52074</v>
       </c>
       <c r="C4" t="n">
-        <v>51680</v>
+        <v>52070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+403</t>
+          <t>+793</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70728</v>
+        <v>71144</v>
       </c>
       <c r="C5" t="n">
-        <v>70692</v>
+        <v>71107</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+335</t>
+          <t>+751</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9326</v>
+        <v>9510</v>
       </c>
       <c r="C6" t="n">
-        <v>9326</v>
+        <v>9510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+124</t>
+          <t>+308</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17091</v>
+        <v>17210</v>
       </c>
       <c r="C7" t="n">
-        <v>17091</v>
+        <v>17210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+118</t>
+          <t>+237</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -578,14 +578,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13135</v>
+        <v>13175</v>
       </c>
       <c r="C8" t="n">
-        <v>12984</v>
+        <v>13024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>+61</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211006</v>
+        <v>212738</v>
       </c>
       <c r="C9" t="n">
-        <v>210776</v>
+        <v>212507</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="D19" t="n">
         <v>3</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D20" t="n">
         <v>4</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D25" t="n">
         <v>4</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
